--- a/docs/data/jp/xlsx/2760.xlsx
+++ b/docs/data/jp/xlsx/2760.xlsx
@@ -6702,7 +6702,7 @@
     <row r="90">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>Provision For Share Based Compensation Expenses For Employees SGA</t>
+          <t>종업원 주식보상 충당금 전입액</t>
         </is>
       </c>
       <c r="C90" s="20" t="n">
@@ -6920,7 +6920,7 @@
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>Guarantee Commission Received NOI</t>
+          <t>수취보증료</t>
         </is>
       </c>
       <c r="I95" s="20" t="n">
@@ -7007,7 +7007,7 @@
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>Compensation For Damage Income NOI</t>
+          <t>수취 손해배상금</t>
         </is>
       </c>
       <c r="E98" s="20" t="n">
@@ -7259,7 +7259,7 @@
     <row r="104">
       <c r="A104" s="18" t="inlineStr">
         <is>
-          <t>Guarantee Commission NOE</t>
+          <t>지급보증료</t>
         </is>
       </c>
       <c r="F104" s="20" t="n">
@@ -7523,7 +7523,7 @@
     <row r="110">
       <c r="A110" s="18" t="inlineStr">
         <is>
-          <t>Gain On Sales Of Investments In Capital Of Subsidiaries And Affiliates EI</t>
+          <t>관계회사 출자금 매각이익</t>
         </is>
       </c>
       <c r="T110" s="20" t="n">
@@ -7720,7 +7720,7 @@
     <row r="115">
       <c r="A115" s="18" t="inlineStr">
         <is>
-          <t>Provision Of Allowance For Doubtful Accounts Of Golf Club Membership EL</t>
+          <t>골프회원권 대손충당금 전입액</t>
         </is>
       </c>
       <c r="T115" s="20" t="n">
@@ -7733,7 +7733,7 @@
     <row r="116">
       <c r="A116" s="18" t="inlineStr">
         <is>
-          <t>Loss On Redemption Of Golf Club Membership EL</t>
+          <t>골프회원권 상환손실</t>
         </is>
       </c>
       <c r="T116" s="20" t="n">
@@ -7746,7 +7746,7 @@
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
-          <t>Provision For Loss On Abolishment Of Trust EL</t>
+          <t>신탁종료손실 충당금 전입액</t>
         </is>
       </c>
       <c r="T117" s="20" t="n">
@@ -7759,7 +7759,7 @@
     <row r="118">
       <c r="A118" s="18" t="inlineStr">
         <is>
-          <t>Loss On Change In Equity EL</t>
+          <t>지분변동 손실</t>
         </is>
       </c>
       <c r="E118" s="20" t="n">
@@ -10692,7 +10692,7 @@
     <row r="177">
       <c r="A177" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Share Based Compensation Expenses For Employees Ope CF</t>
+          <t>종업원 주식보상 충당금 증감액</t>
         </is>
       </c>
       <c r="C177" s="20" t="n">
@@ -10714,7 +10714,7 @@
     <row r="178">
       <c r="A178" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Share Based Compensation Expenses For Directors Ope CF</t>
+          <t>임원 주식보상 충당금 증감액</t>
         </is>
       </c>
       <c r="C178" s="20" t="n">
@@ -10932,7 +10932,7 @@
     <row r="183">
       <c r="A183" s="18" t="inlineStr">
         <is>
-          <t>Loss On Revision Of Retirement Benefit Plan Ope CF</t>
+          <t>퇴직급여제도 개정손실</t>
         </is>
       </c>
       <c r="Q183" s="20" t="n">
@@ -11015,7 +11015,7 @@
     <row r="188">
       <c r="A188" s="18" t="inlineStr">
         <is>
-          <t>Provision For Loss On Abolishment Of Trust Ope CF</t>
+          <t>신탁종료손실 충당금 전입액</t>
         </is>
       </c>
       <c r="S188" s="20" t="n">
@@ -11031,7 +11031,7 @@
     <row r="189">
       <c r="A189" s="18" t="inlineStr">
         <is>
-          <t>Compensation Income For Damage Ope CF</t>
+          <t>수취 손해배상금</t>
         </is>
       </c>
       <c r="D189" s="20" t="n">
@@ -12090,7 +12090,7 @@
     <row r="207">
       <c r="A207" s="18" t="inlineStr">
         <is>
-          <t>Compensation Income For Damage Received Ope CF</t>
+          <t>손해배상금 수취액</t>
         </is>
       </c>
       <c r="D207" s="20" t="n">
@@ -12494,7 +12494,7 @@
     <row r="215">
       <c r="A215" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From The Liquidation Of Subsidiaries And Associates Inv CF</t>
+          <t>관계회사 청산 수입</t>
         </is>
       </c>
       <c r="Q215" s="20" t="n">
@@ -12510,7 +12510,7 @@
     <row r="216">
       <c r="A216" s="18" t="inlineStr">
         <is>
-          <t>Payments For Liquidation Of Subsidiaries And Associates Inv CF</t>
+          <t>관계회사 청산 지출</t>
         </is>
       </c>
       <c r="Q216" s="20" t="n">
@@ -12526,7 +12526,7 @@
     <row r="217">
       <c r="A217" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Sales Of Investments In Capital Of Subsidiaries And Affiliates Inv CF</t>
+          <t>관계회사 출자금 매각 수입</t>
         </is>
       </c>
       <c r="S217" s="20" t="n">
@@ -13066,7 +13066,7 @@
     <row r="229">
       <c r="A229" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Commercial Papers Fin CF</t>
+          <t>기업어음(CP) 순증감액</t>
         </is>
       </c>
       <c r="D229" s="20" t="n">
@@ -17857,7 +17857,7 @@
     <row r="109">
       <c r="A109" s="18" t="inlineStr">
         <is>
-          <t>Commercial Papers Liabilities</t>
+          <t>기업어음(CP)</t>
         </is>
       </c>
       <c r="C109" s="20" t="n">
